--- a/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo et maman entrent dans le magasin. Ça sent le papier et le bois. Hugo voit un petit camion rouge. Il a très envie de le prendre. L'argent est dans le sac de maman. Maman range l'argent. Elle le ferme. Hugo s'arrête. Il dit : maman, je peux l'avoir ? Il demande à l'adulte. Maman, c'est l'adulte. Maman écoute. Elle regarde le camion. Elle dit : aujourd'hui, on achète le pain. Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va demander à papa ou maman.</t>
+          <t>Hugo et maman entrent dans le magasin. Ça sent le papier et le bois. Hugo voit un petit camion rouge. Il a très envie de le prendre. L'argent est dans le sac de maman. Maman range l'argent. Elle le ferme. Hugo s'arrête. Maman, je peux l'avoir ? Il demande à l'adulte. Maman, c'est l'adulte. Maman écoute. Elle regarde le camion. Aujourd'hui, on achète le pain. Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va demander à papa ou maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo et maman entrent dans le magasin. Ça sent le papier et le bois. Hugo voit un petit camion rouge. Il a très envie de le prendre. L'argent est dans le sac de maman. Maman range l'argent. Elle le ferme. Hugo s'arrête.
+narrateur|Maman, je peux l'avoir ? Il demande à l'adulte. Maman, c'est l'adulte. Maman écoute.
+narrateur|Elle regarde le camion.
+narrateur|Aujourd'hui, on achète le pain.
+narrateur|Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va demander à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo veut un camion. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a demandé à l'adulte. Maman a répondu. L'argent est resté dans le sac.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Sur le chemin, Hugo sent le pain chaud. Il tient la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va demander à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1503,7 @@
           <t>narrateur|Hugo veut un camion. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1675,7 @@
           <t>narrateur|Hugo a demandé à l'adulte. Maman a répondu. L'argent est resté dans le sac.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Sur le chemin, Hugo sent le pain chaud. Il tient la main de maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Demander à papa ou maman pour un achat</t>
+          <t>La pelote rouge de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sarah veut une petite pelote rouge à la mercerie. Elle tend la main sans demander. Maman attend la question. Sarah demande. La pelote est à elle.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo et maman entrent dans le magasin. Ça sent le papier et le bois. Hugo voit un petit camion rouge. Il a très envie de le prendre. L'argent est dans le sac de maman. Maman range l'argent. Elle le ferme. Hugo s'arrête. Maman, je peux l'avoir ? Il demande à l'adulte. Maman, c'est l'adulte. Maman écoute. Elle regarde le camion. Aujourd'hui, on achète le pain. Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va demander à papa ou maman.</t>
+          <t>La mercerie sent la laine et le savon. Un rayon perce le verre un peu poussiéreux. Des boutons brillent dans un tiroir. Le bois du comptoir est lisse, usé. Une pelote bleue a perdu un fil. Le fil traîne comme un cheveu. Maman pousse la porte. La clochette fait un tout petit ding. Ça sent la laine ! Oui. On vient chercher du fil. Sarah touche un bouton, tout rond. Il est froid, un peu lisse. En ce moment, Sarah s'arrête devant la vitrine. Une petite pelote rouge attend derrière le verre. Elle est ronde, toute serrée. Elle est rouge. Je la veux. Sarah tend la main. Ses doigts touchent presque la laine. Maman ne bouge pas. Le petit sac reste fermé. Sarah. Tu me demandes ? La main de Sarah s'arrête. La pelote est encore derrière le verre. Oh. Elle rentre les doigts. Maman attend, tout près. On achète si tu demandes. Tu te souviens ? Je peux demander. La clochette s'est tue. Un tiroir sent encore le savon. La laine rouge attend encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo et maman entrent dans le magasin. Ça sent le papier et le bois. Hugo voit un petit camion rouge. Il a très envie de le prendre. L'argent est dans le sac de maman. Maman range l'argent. Elle le ferme. Hugo s'arrête. Il dit : maman, je peux l'avoir ? Il demande à l'adulte. Maman, c'est l'adulte. Maman écoute. Elle regarde le camion. Elle dit : aujourd'hui, on achète le pain. Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va &lt;emphasis level="moderate"&gt;demander&lt;/emphasis&gt; à papa ou maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La mercerie sent la laine et le savon. Un rayon perce le verre un peu poussiéreux. Des boutons brillent dans un tiroir. Le bois du comptoir est lisse, usé. Une pelote bleue a perdu un fil. Le fil traîne comme un cheveu. Maman pousse la porte. La clochette fait un tout petit ding. Ça sent la laine ! Oui. On vient chercher du fil. Sarah touche un bouton, tout rond. Il est froid, un peu lisse. En ce moment, Sarah s'arrête devant la vitrine. Une petite pelote rouge attend derrière le verre. Elle est ronde, toute serrée. Elle est rouge. Je la veux. Sarah tend la main. Ses doigts touchent presque la laine. Maman ne bouge pas. Le petit sac reste fermé. Sarah. Tu me demandes ? La main de Sarah s'arrête. La pelote est encore derrière le verre. Oh. Elle rentre les doigts. Maman attend, tout près. On achète si tu demandes. Tu te souviens ? Je peux demander. La clochette s'est tue. Un tiroir sent encore le savon. La laine rouge attend encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo et maman entrent dans le magasin. Ça sent le papier et le bois. Hugo voit un petit camion rouge. Il a très envie de le prendre. L'argent est dans le sac de maman. Maman range l'argent. Elle le ferme. Hugo s'arrête.
-narrateur|Maman, je peux l'avoir ? Il demande à l'adulte. Maman, c'est l'adulte. Maman écoute.
-narrateur|Elle regarde le camion.
-narrateur|Aujourd'hui, on achète le pain.
-narrateur|Le camion attendra. Hugo sent un petit pincement. Puis il respire. Il a demandé. Maman prend sa main. Ils vont au rayon pain. Hugo porte le pain. L'argent reste dans le sac. Pour un achat, on va demander à papa ou maman.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La mercerie sent la laine et le savon.
+narrateur|Un rayon perce le verre un peu poussiéreux.
+narrateur|Des boutons brillent dans un tiroir.
+narrateur|Le bois du comptoir est lisse, usé.
+narrateur|Une pelote bleue a perdu un fil.
+narrateur|Le fil traîne comme un cheveu.
+narrateur|Maman pousse la porte.
+narrateur|La clochette fait un tout petit ding.
+enfant-f|Ça sent la laine !
+maman|Oui.
+maman|On vient chercher du fil.
+narrateur|Sarah touche un bouton, tout rond.
+narrateur|Il est froid, un peu lisse.
+narrateur|En ce moment, Sarah s'arrête devant la vitrine.
+narrateur|Une petite pelote rouge attend derrière le verre.
+narrateur|Elle est ronde, toute serrée.
+enfant-f|Elle est rouge.
+enfant-f|Je la veux.
+narrateur|Sarah tend la main.
+narrateur|Ses doigts touchent presque la laine.
+narrateur|Maman ne bouge pas.
+narrateur|Le petit sac reste fermé.
+maman|Sarah.
+maman|Tu me demandes ?
+narrateur|La main de Sarah s'arrête.
+narrateur|La pelote est encore derrière le verre.
+enfant-f|Oh.
+narrateur|Elle rentre les doigts.
+narrateur|Maman attend, tout près.
+maman|On achète si tu demandes.
+maman|Tu te souviens ?
+enfant-f|Je peux demander.
+narrateur|La clochette s'est tue.
+narrateur|Un tiroir sent encore le savon.
+narrateur|La laine rouge attend encore.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,12 +1385,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo veut un camion. Que fait-il ?</t>
+          <t>Sarah veut la pelote rouge. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo veut un camion. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut la pelote rouge. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1364,7 +1405,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>demander | il demande | à maman | demander à maman</t>
+          <t>demander | elle demande | elle demande à maman | à maman | s'il te plaît</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1379,7 +1420,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il parle à maman. Que fait Hugo ?</t>
+          <t>Elle demande à maman. Que fait Sarah ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,7 +1469,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1500,10 +1541,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo veut un camion. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Sarah veut la pelote rouge.
+narrateur|Que fait-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1528,12 +1569,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a demandé à l'adulte. Maman a répondu. L'argent est resté dans le sac.</t>
+          <t>Maman, s'il te plaît. Je peux avoir la pelote ? Oui. Merci, Sarah. Tu as demandé. Maman ouvre le petit sac. Elle pose l'argent sur le bois. On lui tend la pelote rouge. Sarah la prend des deux mains. La laine est douce, un peu chaude. Elle est à moi. Oui. Parce que tu as demandé. Sarah serre la pelote contre sa veste. Un fil rouge dépasse un peu. Tu la tiens bien ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo a demandé à l'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt;. Maman a répondu. L'argent est resté dans le sac.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman, s'il te plaît. Je peux avoir la pelote ? Oui. Merci, Sarah. Tu as demandé. Maman ouvre le petit sac. Elle pose l'argent sur le bois. On lui tend la pelote rouge. Sarah la prend des deux mains. La laine est douce, un peu chaude. Elle est à moi. Oui. Parce que tu as demandé. Sarah serre la pelote contre sa veste. Un fil rouge dépasse un peu. Tu la tiens bien ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1596,7 +1637,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1672,10 +1713,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a demandé à l'adulte. Maman a répondu. L'argent est resté dans le sac.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>enfant-f|Maman, s'il te plaît.
+enfant-f|Je peux avoir la pelote ?
+maman|Oui.
+maman|Merci, Sarah.
+maman|Tu as demandé.
+narrateur|Maman ouvre le petit sac.
+narrateur|Elle pose l'argent sur le bois.
+narrateur|On lui tend la pelote rouge.
+narrateur|Sarah la prend des deux mains.
+narrateur|La laine est douce, un peu chaude.
+enfant-f|Elle est à moi.
+maman|Oui.
+maman|Parce que tu as demandé.
+narrateur|Sarah serre la pelote contre sa veste.
+narrateur|Un fil rouge dépasse un peu.
+maman|Tu la tiens bien ?
+enfant-f|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1700,12 +1756,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sur le chemin, Hugo sent le pain chaud. Il tient la main de maman.</t>
+          <t>Elles sortent. La clochette dingue encore une fois. La rue sent le pain, plus loin. Sarah marche avec la pelote. Le fil rouge tape sa manche. On rentre faire un tour de laine ? Oui. Pour le doudou. Tu as demandé avant d'acheter. Bravo. Le soleil est sur le trottoir. La pelote fait une ombre ronde. Sarah sent la laine contre sa veste. Elle est tiède, comme une main.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sur le chemin, Hugo sent le pain chaud. Il tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Elles sortent. La clochette dingue encore une fois. La rue sent le pain, plus loin. Sarah marche avec la pelote. Le fil rouge tape sa manche. On rentre faire un tour de laine ? Oui. Pour le doudou. Tu as demandé avant d'acheter. Bravo. Le soleil est sur le trottoir. La pelote fait une ombre ronde. Sarah sent la laine contre sa veste. Elle est tiède, comme une main.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1768,7 +1824,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1896,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Sur le chemin, Hugo sent le pain chaud. Il tient la main de maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Elles sortent.
+narrateur|La clochette dingue encore une fois.
+narrateur|La rue sent le pain, plus loin.
+narrateur|Sarah marche avec la pelote.
+narrateur|Le fil rouge tape sa manche.
+maman|On rentre faire un tour de laine ?
+enfant-f|Oui.
+enfant-f|Pour le doudou.
+maman|Tu as demandé avant d'acheter.
+maman|Bravo.
+narrateur|Le soleil est sur le trottoir.
+narrateur|La pelote fait une ombre ronde.
+narrateur|Sarah sent la laine contre sa veste.
+narrateur|Elle est tiède, comme une main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1936,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>À la maison, Sarah s'assoit. Elle pose la pelote sur ses genoux. Elle tire un peu de fil. Le rouge court entre ses doigts. Il est doux. Oui. Tu l'as dans les mains. Sarah enroule le fil autour du doudou. Le doudou a maintenant un collier rouge. Il est beau. Il est au chaud. La pelote rouge tourne entre ses doigts.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>À la maison, Sarah s'assoit. Elle pose la pelote sur ses genoux. Elle tire un peu de fil. Le rouge court entre ses doigts. Il est doux. Oui. Tu l'as dans les mains. Sarah enroule le fil autour du doudou. Le doudou a maintenant un collier rouge. Il est beau. Il est au chaud. La pelote rouge tourne entre ses doigts.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1929,14 +1997,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2076,20 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|À la maison, Sarah s'assoit.
+narrateur|Elle pose la pelote sur ses genoux.
+narrateur|Elle tire un peu de fil.
+narrateur|Le rouge court entre ses doigts.
+enfant-f|Il est doux.
+maman|Oui.
+maman|Tu l'as dans les mains.
+narrateur|Sarah enroule le fil autour du doudou.
+narrateur|Le doudou a maintenant un collier rouge.
+enfant-f|Il est beau.
+maman|Il est au chaud.
+narrateur|La pelote rouge tourne entre ses doigts.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2146,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
+++ b/stories/arbres/ATOM-SOC.ARG.002-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>magasin</t>
+          <t>mercerie, tiroirs de bois, vitrine de laine</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
